--- a/output/pdf_financials_xlsx/KG.xlsx
+++ b/output/pdf_financials_xlsx/KG.xlsx
@@ -6376,55 +6376,55 @@
         <v>1.921709</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>2.298834</v>
+        <v>2.308334</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>2.597634</v>
+        <v>2.604209</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.598936</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>3.192676</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>3.437753</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>4.863107</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>4.773456</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>5.37097</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>5.662247</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>6.294864</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>6.422106</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>6.830092</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>6.86337</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>7.111185</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>7.162772</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>7.445469</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>7.504426</v>
       </c>
     </row>
     <row r="93">
@@ -7974,34 +7974,34 @@
         <v>-0.374525</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-0.925697</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>-0.342</v>
+        <v>-2.595356</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-3.434115</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-4.017468</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>-0.666332</v>
+        <v>-4.061933</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0.1</v>
+        <v>-1.207333</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>-2.630928</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0</v>
+        <v>-2.187425</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0</v>
+        <v>-1.665067</v>
       </c>
       <c r="R118" s="3" t="n">
-        <v>0</v>
+        <v>-2.089731</v>
       </c>
       <c r="S118" s="1" t="inlineStr">
         <is>
@@ -10616,7 +10616,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -11482,7 +11486,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -12370,7 +12378,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>
@@ -13496,7 +13508,11 @@
           <t>Reserves (Note 11)</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -20202,7 +20218,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>
@@ -27944,7 +27964,11 @@
           <t>Reserves 2,598,936</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
           <t>-</t>
@@ -32242,7 +32266,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/KG.xlsx
+++ b/output/pdf_financials_xlsx/KG.xlsx
@@ -1143,25 +1143,25 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.012087</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.001969</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000579</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.0009790000000000001</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.003047</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.000831</v>
       </c>
       <c r="I12" s="1" t="inlineStr">
         <is>
@@ -1184,25 +1184,25 @@
         </is>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.032906</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.009287999999999999</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.011669</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.022861</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.051764</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.031841</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>0.0274</v>
       </c>
     </row>
     <row r="13">
@@ -2242,25 +2242,25 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.726098</v>
+        <v>-2.738185</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.403418</v>
+        <v>-1.405387</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.631109</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.399655</v>
+        <v>-2.400234</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.48471</v>
+        <v>-1.485689</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-6.126318</v>
+        <v>-6.129365</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.532184</v>
+        <v>-1.533015</v>
       </c>
       <c r="I27" s="1" t="inlineStr">
         <is>
@@ -2283,25 +2283,25 @@
         </is>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.173867</v>
+        <v>-1.206773</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-1.31632</v>
+        <v>-1.325608</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.627642</v>
+        <v>-0.639311</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-1.029828</v>
+        <v>-1.052689</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.845957</v>
+        <v>-0.897721</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-0.950424</v>
+        <v>-0.9822650000000001</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>-0.985085</v>
+        <v>-1.012485</v>
       </c>
     </row>
     <row r="28">
@@ -2380,25 +2380,25 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.726098</v>
+        <v>-2.738185</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.403418</v>
+        <v>-1.405387</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.618988</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.397226</v>
+        <v>-2.397805</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.420921</v>
+        <v>-1.4219</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-6.015557</v>
+        <v>-6.018604</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.410918</v>
+        <v>-1.411749</v>
       </c>
       <c r="I29" s="1" t="inlineStr">
         <is>
@@ -2421,25 +2421,25 @@
         </is>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.013705</v>
+        <v>-1.046611</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-1.1692</v>
+        <v>-1.178488</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.484448</v>
+        <v>-0.496117</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.8875999999999999</v>
+        <v>-0.910461</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.703729</v>
+        <v>-0.755493</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-0.808164</v>
+        <v>-0.840005</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-0.985085</v>
+        <v>-1.012485</v>
       </c>
     </row>
     <row r="30">
@@ -2719,19 +2719,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.016787</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.56047</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.687887</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>3.924521</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.096304</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0.073681</v>
@@ -2755,22 +2755,22 @@
         <v>0.133949</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>2.853355</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>2.670335</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.115785</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>1.009695</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.07938199999999999</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>3.331187</v>
       </c>
     </row>
     <row r="35">
@@ -2841,19 +2841,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.016787</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.56047</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.687887</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>3.924521</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.096304</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>0.073681</v>
@@ -2877,22 +2877,22 @@
         <v>0.133949</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>2.853355</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>2.670335</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.115785</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>1.009695</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.07938199999999999</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>3.331187</v>
       </c>
     </row>
     <row r="37">
@@ -3573,19 +3573,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.277904</v>
+        <v>0.261117</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.601848</v>
+        <v>0.041378</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.769867</v>
+        <v>0.08198</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>4.015609</v>
+        <v>0.091088</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.320779</v>
+        <v>0.224475</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0.039116</v>
@@ -3609,22 +3609,22 @@
         <v>0.221454</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>3.143258</v>
+        <v>0.289903</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>2.952946</v>
+        <v>0.282611</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.201115</v>
+        <v>0.08533</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>1.104824</v>
+        <v>0.09512900000000001</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.186205</v>
+        <v>0.106823</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>3.490206</v>
+        <v>0.159019</v>
       </c>
     </row>
     <row r="49">
@@ -8364,22 +8364,22 @@
         <v>0</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.122312</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.156416</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.145613</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.147847</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.163724</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>0</v>
+        <v>-0.16616</v>
       </c>
       <c r="S124" s="1" t="inlineStr">
         <is>
@@ -8427,22 +8427,22 @@
         <v>0</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.122312</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.156416</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.145613</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.147847</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.163724</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>-0.16616</v>
       </c>
       <c r="S125" s="1" t="inlineStr">
         <is>
@@ -9288,7 +9288,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -23162,7 +23162,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E138" s="5" t="n">
@@ -26384,7 +26384,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -32074,7 +32074,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E224" t="inlineStr">
         <is>
           <t>-</t>
@@ -51902,7 +51906,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E415" s="5" t="n">
@@ -62132,7 +62136,7 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">

--- a/output/pdf_financials_xlsx/KG.xlsx
+++ b/output/pdf_financials_xlsx/KG.xlsx
@@ -6882,19 +6882,19 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.062527</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>0.222495</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.012645</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>0.008573000000000001</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>-0.027105</v>
+        <v>-0.020576</v>
       </c>
       <c r="G101" s="3" t="n">
         <v>-0.002763</v>
@@ -7197,19 +7197,19 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-0.107551</v>
+        <v>-0.170078</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-0.087144</v>
+        <v>0.135351</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.413395</v>
+        <v>-0.42604</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>-0.038333</v>
+        <v>-0.02976</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0.206054</v>
+        <v>0.212583</v>
       </c>
       <c r="G106" s="3" t="n">
         <v>0.179278</v>
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.103936</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.002525</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.032879</v>
       </c>
       <c r="E115" s="3" t="n">
         <v>0</v>
@@ -39924,7 +39924,11 @@
           <t>Shares issued for cash (Note 12(b))</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr"/>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr">
         <is>
           <t>-</t>
@@ -41624,7 +41628,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr"/>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E316" t="inlineStr">
         <is>
           <t>-</t>
@@ -42260,7 +42268,11 @@
           <t>Shares issued for cash (Note 13(b))</t>
         </is>
       </c>
-      <c r="D322" t="inlineStr"/>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E322" t="inlineStr">
         <is>
           <t>-</t>
@@ -44900,7 +44912,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D347" t="inlineStr"/>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E347" t="inlineStr">
         <is>
           <t>-</t>
@@ -45104,7 +45120,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D349" t="inlineStr"/>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E349" s="5" t="n">
         <v>-0.062527</v>
       </c>
@@ -46420,7 +46440,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D362" t="inlineStr"/>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E362" s="5" t="n">
         <v>0.9305</v>
       </c>
@@ -47440,7 +47464,11 @@
           <t>HST recoverable</t>
         </is>
       </c>
-      <c r="D372" t="inlineStr"/>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E372" t="inlineStr">
         <is>
           <t>-</t>
@@ -48594,7 +48622,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D383" t="inlineStr"/>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E383" s="5" t="n">
         <v>0.103936</v>
       </c>
@@ -60160,7 +60192,11 @@
           <t>Deferred Income Tax Recovery (Note 17)</t>
         </is>
       </c>
-      <c r="D494" t="inlineStr"/>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E494" t="inlineStr">
         <is>
           <t>-</t>
